--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -2182,7 +2182,7 @@
         <v>125221075</v>
       </c>
       <c r="B16" t="n">
-        <v>91579</v>
+        <v>91737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2177,112 +2177,6 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>125221075</v>
-      </c>
-      <c r="B16" t="n">
-        <v>91737</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>760</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Doftticka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Haploporus odorus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Tallträsk, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>650943</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7168309</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2177,6 +2177,116 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125221075</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91799</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>760</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tallträsk, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>650943</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7168309</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -2182,7 +2182,7 @@
         <v>125221075</v>
       </c>
       <c r="B16" t="n">
-        <v>91799</v>
+        <v>91802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -2182,7 +2182,7 @@
         <v>125221075</v>
       </c>
       <c r="B16" t="n">
-        <v>91802</v>
+        <v>91806</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -2182,7 +2182,7 @@
         <v>125221075</v>
       </c>
       <c r="B16" t="n">
-        <v>91806</v>
+        <v>91808</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -2182,7 +2182,7 @@
         <v>125221075</v>
       </c>
       <c r="B16" t="n">
-        <v>91808</v>
+        <v>91810</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -2182,7 +2182,7 @@
         <v>125221075</v>
       </c>
       <c r="B16" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -2182,7 +2182,7 @@
         <v>125221075</v>
       </c>
       <c r="B16" t="n">
-        <v>91812</v>
+        <v>91816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24512-2025 artfynd.xlsx
+++ b/artfynd/A 24512-2025 artfynd.xlsx
@@ -2182,7 +2182,7 @@
         <v>125221075</v>
       </c>
       <c r="B16" t="n">
-        <v>91816</v>
+        <v>91819</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
